--- a/artfynd/A 62314-2019 artfynd.xlsx
+++ b/artfynd/A 62314-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62314-2019 artfynd.xlsx
+++ b/artfynd/A 62314-2019 artfynd.xlsx
@@ -1944,7 +1944,7 @@
         <v>80118757</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412514.5980939919</v>
+        <v>412515</v>
       </c>
       <c r="R13" t="n">
-        <v>6714117.926228293</v>
+        <v>6714118</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,19 +2022,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62314-2019 artfynd.xlsx
+++ b/artfynd/A 62314-2019 artfynd.xlsx
@@ -1944,7 +1944,7 @@
         <v>80118757</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
